--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
   <si>
     <t>No.</t>
   </si>
@@ -35,25 +35,43 @@
     <t>평균</t>
   </si>
   <si>
+    <t>541.1</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
     <t>521.5</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>5.2</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>560.8</t>
+  </si>
+  <si>
+    <t>1082.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>03일</t>
   </si>
   <si>
     <t>04일</t>
@@ -448,16 +466,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s" s="31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -465,19 +483,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -485,19 +503,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -505,19 +523,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -525,19 +543,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -545,19 +563,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -565,19 +583,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -585,19 +603,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -605,19 +623,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -625,19 +643,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -645,19 +663,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -665,19 +683,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -685,19 +703,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -705,19 +723,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -725,19 +743,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -745,19 +763,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -765,19 +783,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -785,19 +803,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -805,19 +823,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -825,19 +843,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -845,19 +863,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -865,19 +883,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -885,19 +903,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -905,19 +923,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -925,19 +943,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -945,19 +963,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -965,19 +983,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -985,19 +1003,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1005,19 +1023,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1025,19 +1043,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1045,19 +1063,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>541.1</t>
+    <t>489.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.4</t>
+    <t>4.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -71,10 +71,22 @@
     <t>03일</t>
   </si>
   <si>
+    <t>386.2</t>
+  </si>
+  <si>
+    <t>1468.5</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>14.7</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>04일</t>
   </si>
   <si>
     <t>05일</t>
@@ -509,13 +521,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -523,19 +535,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -543,19 +555,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -563,19 +575,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -583,19 +595,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -603,19 +615,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -623,19 +635,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -643,19 +655,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -663,19 +675,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -683,19 +695,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -703,19 +715,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -723,19 +735,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -743,19 +755,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -763,19 +775,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -783,19 +795,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -803,19 +815,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -823,19 +835,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -843,19 +855,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="55">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>489.5</t>
+    <t>490.0</t>
   </si>
   <si>
     <t>-</t>
@@ -86,10 +86,19 @@
     <t>04일</t>
   </si>
   <si>
+    <t>491.6</t>
+  </si>
+  <si>
+    <t>1960.1</t>
+  </si>
+  <si>
+    <t>19.6</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>05일</t>
   </si>
   <si>
     <t>06일</t>
@@ -541,13 +550,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -555,19 +564,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -575,19 +584,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -595,19 +604,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -615,19 +624,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -635,19 +644,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -655,19 +664,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -675,19 +684,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -695,19 +704,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -715,19 +724,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -735,19 +744,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -755,19 +764,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -775,19 +784,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -795,19 +804,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -815,19 +824,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -835,19 +844,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -855,19 +864,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -875,19 +884,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -895,19 +904,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -915,19 +924,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -935,19 +944,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -955,19 +964,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -975,19 +984,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -995,19 +1004,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1015,19 +1024,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1035,19 +1044,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1055,19 +1064,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1075,19 +1084,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="60">
   <si>
     <t>No.</t>
   </si>
@@ -35,73 +35,88 @@
     <t>평균</t>
   </si>
   <si>
-    <t>490.0</t>
+    <t>456.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>521.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>560.8</t>
+  </si>
+  <si>
+    <t>1082.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>386.2</t>
+  </si>
+  <si>
+    <t>1468.5</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>14.7</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>491.6</t>
+  </si>
+  <si>
+    <t>1960.1</t>
+  </si>
+  <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>521.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>560.8</t>
-  </si>
-  <si>
-    <t>1082.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>10.8</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>386.2</t>
-  </si>
-  <si>
-    <t>1468.5</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>14.7</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>491.6</t>
-  </si>
-  <si>
-    <t>1960.1</t>
-  </si>
-  <si>
     <t>19.6</t>
   </si>
   <si>
     <t>05일</t>
   </si>
   <si>
+    <t>320.9</t>
+  </si>
+  <si>
+    <t>2281.0</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>06일</t>
   </si>
   <si>
     <t>07일</t>
@@ -553,10 +568,10 @@
         <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -564,19 +579,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -584,19 +599,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -604,19 +619,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -624,19 +639,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -644,19 +659,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -664,19 +679,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -684,19 +699,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -704,19 +719,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -724,19 +739,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -744,19 +759,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -764,19 +779,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -784,19 +799,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -804,19 +819,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -824,19 +839,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -844,19 +859,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -864,19 +879,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -884,19 +899,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -904,19 +919,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -924,19 +939,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -944,19 +959,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -964,19 +979,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -984,19 +999,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1004,19 +1019,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1024,19 +1039,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1044,19 +1059,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1064,19 +1079,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1084,19 +1099,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>456.2</t>
+    <t>472.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
+    <t>4.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -116,10 +116,22 @@
     <t>06일</t>
   </si>
   <si>
+    <t>550.9</t>
+  </si>
+  <si>
+    <t>2831.9</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -605,13 +617,13 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -619,19 +631,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -639,19 +651,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -659,19 +671,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -679,19 +691,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -699,19 +711,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -719,19 +731,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -739,19 +751,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -759,19 +771,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -779,19 +791,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -799,19 +811,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -819,19 +831,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -839,19 +851,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -859,19 +871,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -879,19 +891,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -899,19 +911,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -919,19 +931,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -939,19 +951,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -959,19 +971,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -979,19 +991,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -999,19 +1011,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1019,19 +1031,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1039,19 +1051,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1059,19 +1071,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1079,19 +1091,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1099,19 +1111,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>472.0</t>
+    <t>479.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -131,10 +131,22 @@
     <t>07일</t>
   </si>
   <si>
+    <t>526.9</t>
+  </si>
+  <si>
+    <t>3358.8</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
   </si>
   <si>
     <t>09일</t>
@@ -637,13 +649,13 @@
         <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -651,19 +663,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -671,19 +683,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -691,19 +703,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -711,19 +723,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -731,19 +743,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -751,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -771,19 +783,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -791,19 +803,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -811,19 +823,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -831,19 +843,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -851,19 +863,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -871,19 +883,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -891,19 +903,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -911,19 +923,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -931,19 +943,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -951,19 +963,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -971,19 +983,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -991,19 +1003,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1011,19 +1023,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1031,19 +1043,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1051,19 +1063,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1071,19 +1083,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1091,19 +1103,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1111,19 +1123,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="70">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>479.8</t>
+    <t>485.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -92,9 +92,6 @@
     <t>1960.1</t>
   </si>
   <si>
-    <t>4.9</t>
-  </si>
-  <si>
     <t>19.6</t>
   </si>
   <si>
@@ -146,10 +143,19 @@
     <t>08일</t>
   </si>
   <si>
+    <t>524.7</t>
+  </si>
+  <si>
+    <t>3883.5</t>
+  </si>
+  <si>
+    <t>38.8</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
   </si>
   <si>
     <t>10일</t>
@@ -592,10 +598,10 @@
         <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -603,19 +609,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -623,19 +629,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>35</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>36</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -643,19 +649,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>38</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>39</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>40</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>41</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -663,19 +669,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>43</v>
-      </c>
-      <c r="C10" t="s" s="36">
-        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
         <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -683,19 +689,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -703,19 +709,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -723,19 +729,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -743,19 +749,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -763,19 +769,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -783,19 +789,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -803,19 +809,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -823,19 +829,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -843,19 +849,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -863,19 +869,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -883,19 +889,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -903,19 +909,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -923,19 +929,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -943,19 +949,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -963,19 +969,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -983,19 +989,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1003,19 +1009,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1023,19 +1029,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1043,19 +1049,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1063,19 +1069,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1083,19 +1089,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1103,19 +1109,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1123,19 +1129,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="75">
   <si>
     <t>No.</t>
   </si>
@@ -35,63 +35,66 @@
     <t>평균</t>
   </si>
   <si>
-    <t>485.4</t>
+    <t>481.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>521.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>560.8</t>
+  </si>
+  <si>
+    <t>1082.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>386.2</t>
+  </si>
+  <si>
+    <t>1468.5</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>14.7</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>491.6</t>
+  </si>
+  <si>
+    <t>1960.1</t>
+  </si>
+  <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>521.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>560.8</t>
-  </si>
-  <si>
-    <t>1082.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>10.8</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>386.2</t>
-  </si>
-  <si>
-    <t>1468.5</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>14.7</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>491.6</t>
-  </si>
-  <si>
-    <t>1960.1</t>
-  </si>
-  <si>
     <t>19.6</t>
   </si>
   <si>
@@ -155,10 +158,22 @@
     <t>09일</t>
   </si>
   <si>
+    <t>446.7</t>
+  </si>
+  <si>
+    <t>4330.2</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>43.3</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -598,10 +613,10 @@
         <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -609,19 +624,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -629,19 +644,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -649,19 +664,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -669,19 +684,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
         <v>12</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -689,19 +704,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -709,19 +724,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -729,19 +744,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -749,19 +764,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -769,19 +784,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -789,19 +804,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -809,19 +824,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -829,19 +844,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -849,19 +864,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -869,19 +884,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -889,19 +904,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -909,19 +924,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -929,19 +944,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -949,19 +964,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -969,19 +984,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -989,19 +1004,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1009,19 +1024,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1029,19 +1044,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1049,19 +1064,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1069,19 +1084,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1089,19 +1104,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1109,19 +1124,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1129,19 +1144,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>481.1</t>
+    <t>483.9</t>
   </si>
   <si>
     <t>-</t>
@@ -173,10 +173,22 @@
     <t>10일</t>
   </si>
   <si>
+    <t>508.7</t>
+  </si>
+  <si>
+    <t>4838.9</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>11일</t>
   </si>
   <si>
     <t>12일</t>
@@ -730,13 +742,13 @@
         <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -744,19 +756,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -764,19 +776,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -784,19 +796,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -804,19 +816,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -824,19 +836,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -844,19 +856,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -864,19 +876,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -884,19 +896,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -904,19 +916,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -924,19 +936,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -944,19 +956,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -964,19 +976,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -984,19 +996,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1004,19 +1016,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1024,19 +1036,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1044,19 +1056,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1064,19 +1076,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1084,19 +1096,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1104,19 +1116,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1124,19 +1136,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1144,19 +1156,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="87">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>483.9</t>
+    <t>469.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -188,13 +188,37 @@
     <t>11일</t>
   </si>
   <si>
+    <t>373.0</t>
+  </si>
+  <si>
+    <t>5211.9</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>52.1</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>425.8</t>
+  </si>
+  <si>
+    <t>5637.7</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>56.4</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -762,13 +786,13 @@
         <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -776,19 +800,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -796,19 +820,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -816,19 +840,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -836,19 +860,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -856,19 +880,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -876,19 +900,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -896,19 +920,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -916,19 +940,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -936,19 +960,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -956,19 +980,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -976,19 +1000,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -996,19 +1020,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1016,19 +1040,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1036,19 +1060,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1056,19 +1080,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1076,19 +1100,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1096,19 +1120,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1116,19 +1140,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1136,19 +1160,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1156,19 +1180,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="91">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>469.8</t>
+    <t>444.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.4</t>
   </si>
   <si>
     <t>01일</t>
@@ -218,10 +218,22 @@
     <t>13일</t>
   </si>
   <si>
+    <t>146.6</t>
+  </si>
+  <si>
+    <t>5784.3</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>57.8</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -826,13 +838,13 @@
         <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -840,19 +852,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -860,19 +872,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -880,19 +892,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -900,19 +912,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -920,19 +932,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -940,19 +952,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -960,19 +972,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -980,19 +992,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1000,19 +1012,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1020,19 +1032,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1040,19 +1052,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1060,19 +1072,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1080,19 +1092,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1100,19 +1112,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1120,19 +1132,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1140,19 +1152,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1160,19 +1172,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1180,19 +1192,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="94">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>444.9</t>
+    <t>452.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.5</t>
   </si>
   <si>
     <t>01일</t>
@@ -164,9 +164,6 @@
     <t>4330.2</t>
   </si>
   <si>
-    <t>4.5</t>
-  </si>
-  <si>
     <t>43.3</t>
   </si>
   <si>
@@ -233,10 +230,22 @@
     <t>14일</t>
   </si>
   <si>
+    <t>544.6</t>
+  </si>
+  <si>
+    <t>6328.9</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>63.3</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -761,10 +770,10 @@
         <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -772,19 +781,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>54</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -792,19 +801,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>59</v>
       </c>
-      <c r="E13" t="s" s="33">
+      <c r="F13" t="s" s="34">
         <v>60</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -812,19 +821,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>62</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>63</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>64</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -832,19 +841,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>69</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>70</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -852,19 +861,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>72</v>
-      </c>
-      <c r="C16" t="s" s="36">
-        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
         <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -872,19 +881,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -892,19 +901,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -912,19 +921,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -932,19 +941,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -952,19 +961,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -972,19 +981,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -992,19 +1001,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1012,19 +1021,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1032,19 +1041,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1052,19 +1061,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1072,19 +1081,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1092,19 +1101,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1112,19 +1121,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1132,19 +1141,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1152,19 +1161,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1172,19 +1181,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1192,19 +1201,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="98">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>452.1</t>
+    <t>446.3</t>
   </si>
   <si>
     <t>-</t>
@@ -245,10 +245,22 @@
     <t>15일</t>
   </si>
   <si>
+    <t>364.9</t>
+  </si>
+  <si>
+    <t>6693.8</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>66.9</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -887,13 +899,13 @@
         <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -901,19 +913,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -921,19 +933,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -941,19 +953,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -961,19 +973,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -981,19 +993,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1001,19 +1013,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1021,19 +1033,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1041,19 +1053,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1061,19 +1073,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1081,19 +1093,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1101,19 +1113,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1121,19 +1133,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1141,19 +1153,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1161,19 +1173,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1181,19 +1193,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1201,19 +1213,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
   <si>
     <t>No.</t>
   </si>
@@ -245,13 +245,10 @@
     <t>15일</t>
   </si>
   <si>
-    <t>364.9</t>
-  </si>
-  <si>
-    <t>6693.8</t>
-  </si>
-  <si>
-    <t>3.6</t>
+    <t>365.1</t>
+  </si>
+  <si>
+    <t>6694.0</t>
   </si>
   <si>
     <t>66.9</t>
@@ -902,10 +899,10 @@
         <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s" s="34">
         <v>79</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>80</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -913,19 +910,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -933,19 +930,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -953,19 +950,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -973,19 +970,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -993,19 +990,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1013,19 +1010,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1033,19 +1030,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1053,19 +1050,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1073,19 +1070,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1093,19 +1090,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1113,19 +1110,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1133,19 +1130,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1153,19 +1150,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1173,19 +1170,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1193,19 +1190,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1213,19 +1210,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="102">
   <si>
     <t>No.</t>
   </si>
@@ -35,135 +35,138 @@
     <t>평균</t>
   </si>
   <si>
-    <t>446.3</t>
+    <t>435.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>521.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>560.8</t>
+  </si>
+  <si>
+    <t>1082.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>386.2</t>
+  </si>
+  <si>
+    <t>1468.5</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>14.7</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>491.6</t>
+  </si>
+  <si>
+    <t>1960.1</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>19.6</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>320.9</t>
+  </si>
+  <si>
+    <t>2281.0</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>550.9</t>
+  </si>
+  <si>
+    <t>2831.9</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>526.9</t>
+  </si>
+  <si>
+    <t>3358.8</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>524.7</t>
+  </si>
+  <si>
+    <t>3883.5</t>
+  </si>
+  <si>
+    <t>38.8</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>446.7</t>
+  </si>
+  <si>
+    <t>4330.2</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>521.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>560.8</t>
-  </si>
-  <si>
-    <t>1082.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>10.8</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>386.2</t>
-  </si>
-  <si>
-    <t>1468.5</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>14.7</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>491.6</t>
-  </si>
-  <si>
-    <t>1960.1</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>19.6</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>320.9</t>
-  </si>
-  <si>
-    <t>2281.0</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>22.8</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>550.9</t>
-  </si>
-  <si>
-    <t>2831.9</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>526.9</t>
-  </si>
-  <si>
-    <t>3358.8</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>33.6</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>524.7</t>
-  </si>
-  <si>
-    <t>3883.5</t>
-  </si>
-  <si>
-    <t>38.8</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>446.7</t>
-  </si>
-  <si>
-    <t>4330.2</t>
-  </si>
-  <si>
     <t>43.3</t>
   </si>
   <si>
@@ -257,10 +260,22 @@
     <t>16일</t>
   </si>
   <si>
+    <t>279.1</t>
+  </si>
+  <si>
+    <t>6973.1</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>69.7</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -779,10 +794,10 @@
         <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -790,19 +805,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -810,19 +825,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -830,19 +845,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -850,19 +865,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -870,19 +885,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -890,19 +905,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -910,19 +925,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -930,19 +945,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -950,19 +965,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -970,19 +985,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -990,19 +1005,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1010,19 +1025,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1030,19 +1045,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1050,19 +1065,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1070,19 +1085,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1090,19 +1105,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1110,19 +1125,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1130,19 +1145,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1150,19 +1165,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1170,19 +1185,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1190,19 +1205,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1210,19 +1225,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -260,10 +260,10 @@
     <t>16일</t>
   </si>
   <si>
-    <t>279.1</t>
-  </si>
-  <si>
-    <t>6973.1</t>
+    <t>279.4</t>
+  </si>
+  <si>
+    <t>6973.4</t>
   </si>
   <si>
     <t>2.8</t>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>435.8</t>
+    <t>437.3</t>
   </si>
   <si>
     <t>-</t>
@@ -275,10 +275,22 @@
     <t>17일</t>
   </si>
   <si>
+    <t>460.6</t>
+  </si>
+  <si>
+    <t>7434.0</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>74.3</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -951,13 +963,13 @@
         <v>87</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -965,19 +977,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -985,19 +997,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1005,19 +1017,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1025,19 +1037,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1045,19 +1057,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1065,19 +1077,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1085,19 +1097,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1105,19 +1117,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1125,19 +1137,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1145,19 +1157,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1165,19 +1177,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1185,19 +1197,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1205,19 +1217,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1225,19 +1237,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>437.3</t>
+    <t>437.4</t>
   </si>
   <si>
     <t>-</t>
@@ -275,16 +275,16 @@
     <t>17일</t>
   </si>
   <si>
-    <t>460.6</t>
-  </si>
-  <si>
-    <t>7434.0</t>
+    <t>461.8</t>
+  </si>
+  <si>
+    <t>7435.2</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>74.3</t>
+    <t>74.4</t>
   </si>
   <si>
     <t>18일</t>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>437.4</t>
+    <t>416.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -290,10 +290,22 @@
     <t>18일</t>
   </si>
   <si>
+    <t>55.0</t>
+  </si>
+  <si>
+    <t>7490.2</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>74.9</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -983,13 +995,13 @@
         <v>92</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -997,19 +1009,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1017,19 +1029,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1037,19 +1049,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1057,19 +1069,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1077,19 +1089,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1097,19 +1109,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1117,19 +1129,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1137,19 +1149,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1157,19 +1169,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1177,19 +1189,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1197,19 +1209,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1217,19 +1229,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1237,19 +1249,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>416.1</t>
+    <t>408.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.2</t>
+    <t>4.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -305,10 +305,22 @@
     <t>19일</t>
   </si>
   <si>
+    <t>270.6</t>
+  </si>
+  <si>
+    <t>7760.8</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>77.6</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
   </si>
   <si>
     <t>21일</t>
@@ -1015,13 +1027,13 @@
         <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1029,19 +1041,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1049,19 +1061,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1069,19 +1081,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1089,19 +1101,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1109,19 +1121,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1129,19 +1141,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1149,19 +1161,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1169,19 +1181,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1189,19 +1201,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1209,19 +1221,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1229,19 +1241,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1249,19 +1261,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>408.5</t>
+    <t>407.1</t>
   </si>
   <si>
     <t>-</t>
@@ -320,10 +320,22 @@
     <t>20일</t>
   </si>
   <si>
+    <t>380.8</t>
+  </si>
+  <si>
+    <t>8141.6</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>81.4</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -1047,13 +1059,13 @@
         <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1061,19 +1073,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1081,19 +1093,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1101,19 +1113,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1121,19 +1133,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1141,19 +1153,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1161,19 +1173,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1181,19 +1193,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1201,19 +1213,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1221,19 +1233,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1241,19 +1253,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1261,19 +1273,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="122">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>407.1</t>
+    <t>403.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.1</t>
+    <t>4.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -335,10 +335,22 @@
     <t>21일</t>
   </si>
   <si>
+    <t>339.9</t>
+  </si>
+  <si>
+    <t>8481.5</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>84.8</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -1079,13 +1091,13 @@
         <v>107</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1093,19 +1105,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1113,19 +1125,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1133,19 +1145,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1153,19 +1165,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1173,19 +1185,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1193,19 +1205,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1213,19 +1225,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1233,19 +1245,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1253,19 +1265,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1273,19 +1285,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="125">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>403.9</t>
+    <t>409.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.0</t>
+    <t>4.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -350,10 +350,19 @@
     <t>22일</t>
   </si>
   <si>
+    <t>526.4</t>
+  </si>
+  <si>
+    <t>9007.9</t>
+  </si>
+  <si>
+    <t>90.1</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
   </si>
   <si>
     <t>24일</t>
@@ -1111,13 +1120,13 @@
         <v>112</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1125,19 +1134,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1145,19 +1154,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1165,19 +1174,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1185,19 +1194,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1205,19 +1214,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1225,19 +1234,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1245,19 +1254,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1265,19 +1274,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1285,19 +1294,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="129">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>409.5</t>
+    <t>410.7</t>
   </si>
   <si>
     <t>-</t>
@@ -362,10 +362,22 @@
     <t>23일</t>
   </si>
   <si>
+    <t>438.6</t>
+  </si>
+  <si>
+    <t>9446.5</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>94.5</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -1140,13 +1152,13 @@
         <v>116</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1154,19 +1166,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1174,19 +1186,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1194,19 +1206,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1214,19 +1226,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1234,19 +1246,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1254,19 +1266,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1274,19 +1286,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1294,19 +1306,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>410.7</t>
+    <t>394.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.1</t>
+    <t>3.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -77,9 +77,6 @@
     <t>1468.5</t>
   </si>
   <si>
-    <t>3.9</t>
-  </si>
-  <si>
     <t>14.7</t>
   </si>
   <si>
@@ -377,10 +374,22 @@
     <t>24일</t>
   </si>
   <si>
+    <t>26.9</t>
+  </si>
+  <si>
+    <t>9473.4</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>94.7</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -755,10 +764,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -766,19 +775,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -786,19 +795,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -806,19 +815,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>35</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>36</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -826,19 +835,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>38</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>39</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>40</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>41</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -846,19 +855,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>43</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>44</v>
-      </c>
-      <c r="D10" t="s" s="37">
-        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
         <v>12</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -866,19 +875,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>47</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>48</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>49</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -886,19 +895,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>54</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -906,19 +915,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>59</v>
       </c>
-      <c r="E13" t="s" s="33">
+      <c r="F13" t="s" s="34">
         <v>60</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -926,19 +935,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>62</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>63</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>64</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -946,19 +955,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>69</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>70</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -966,19 +975,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>72</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>73</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>74</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>75</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>76</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -986,19 +995,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>77</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>78</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s" s="34">
         <v>79</v>
-      </c>
-      <c r="E17" t="s" s="33">
-        <v>60</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>80</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1006,19 +1015,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>81</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>82</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
         <v>83</v>
       </c>
-      <c r="E18" t="s" s="38">
+      <c r="F18" t="s" s="39">
         <v>84</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>85</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1026,19 +1035,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>86</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>87</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>88</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>89</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>90</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1046,19 +1055,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>91</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>92</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
         <v>93</v>
       </c>
-      <c r="E20" t="s" s="38">
+      <c r="F20" t="s" s="39">
         <v>94</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1066,19 +1075,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>96</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>97</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>98</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>99</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1086,19 +1095,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>101</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>102</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>103</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>104</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>105</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1106,19 +1115,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>106</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>107</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
         <v>108</v>
       </c>
-      <c r="E23" t="s" s="33">
+      <c r="F23" t="s" s="34">
         <v>109</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>110</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1126,19 +1135,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>110</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>111</v>
       </c>
-      <c r="C24" t="s" s="36">
+      <c r="D24" t="s" s="37">
         <v>112</v>
       </c>
-      <c r="D24" t="s" s="37">
+      <c r="E24" t="s" s="38">
+        <v>40</v>
+      </c>
+      <c r="F24" t="s" s="39">
         <v>113</v>
-      </c>
-      <c r="E24" t="s" s="38">
-        <v>41</v>
-      </c>
-      <c r="F24" t="s" s="39">
-        <v>114</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1146,19 +1155,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
+        <v>114</v>
+      </c>
+      <c r="C25" t="s" s="31">
         <v>115</v>
       </c>
-      <c r="C25" t="s" s="31">
+      <c r="D25" t="s" s="32">
         <v>116</v>
       </c>
-      <c r="D25" t="s" s="32">
+      <c r="E25" t="s" s="33">
         <v>117</v>
       </c>
-      <c r="E25" t="s" s="33">
+      <c r="F25" t="s" s="34">
         <v>118</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>119</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1166,19 +1175,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>119</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>120</v>
-      </c>
-      <c r="C26" t="s" s="36">
-        <v>121</v>
       </c>
       <c r="D26" t="s" s="37">
         <v>121</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1186,19 +1195,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1206,19 +1215,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1226,19 +1235,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1246,19 +1255,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1266,19 +1275,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1286,19 +1295,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1306,19 +1315,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="136">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>394.7</t>
+    <t>386.1</t>
   </si>
   <si>
     <t>-</t>
@@ -389,10 +389,22 @@
     <t>25일</t>
   </si>
   <si>
+    <t>179.7</t>
+  </si>
+  <si>
+    <t>9653.1</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>96.5</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -1201,13 +1213,13 @@
         <v>125</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1215,19 +1227,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1235,19 +1247,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1255,19 +1267,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1275,19 +1287,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1295,19 +1307,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1315,19 +1327,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="140">
   <si>
     <t>No.</t>
   </si>
@@ -35,48 +35,51 @@
     <t>평균</t>
   </si>
   <si>
-    <t>386.1</t>
+    <t>380.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>521.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>560.8</t>
+  </si>
+  <si>
+    <t>1082.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>386.2</t>
+  </si>
+  <si>
+    <t>1468.5</t>
+  </si>
+  <si>
     <t>3.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>521.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>560.8</t>
-  </si>
-  <si>
-    <t>1082.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>10.8</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>386.2</t>
-  </si>
-  <si>
-    <t>1468.5</t>
-  </si>
-  <si>
     <t>14.7</t>
   </si>
   <si>
@@ -323,9 +326,6 @@
     <t>8141.6</t>
   </si>
   <si>
-    <t>3.8</t>
-  </si>
-  <si>
     <t>81.4</t>
   </si>
   <si>
@@ -404,10 +404,22 @@
     <t>26일</t>
   </si>
   <si>
+    <t>243.4</t>
+  </si>
+  <si>
+    <t>9896.5</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>99.0</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
   </si>
   <si>
     <t>28일</t>
@@ -776,10 +788,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -787,19 +799,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -807,19 +819,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -827,19 +839,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -847,19 +859,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -867,19 +879,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
         <v>12</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -887,19 +899,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -907,19 +919,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -927,19 +939,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -947,19 +959,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -967,19 +979,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -987,19 +999,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1007,19 +1019,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1027,19 +1039,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1047,19 +1059,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1067,19 +1079,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1087,19 +1099,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1107,16 +1119,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s" s="39">
         <v>104</v>
@@ -1156,7 +1168,7 @@
         <v>112</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s" s="39">
         <v>113</v>
@@ -1233,13 +1245,13 @@
         <v>130</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1247,19 +1259,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1267,19 +1279,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1287,19 +1299,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1307,19 +1319,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1327,19 +1339,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="143">
   <si>
     <t>No.</t>
   </si>
@@ -35,297 +35,297 @@
     <t>평균</t>
   </si>
   <si>
-    <t>380.6</t>
+    <t>385.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>521.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>560.8</t>
+  </si>
+  <si>
+    <t>1082.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>386.2</t>
+  </si>
+  <si>
+    <t>1468.5</t>
+  </si>
+  <si>
+    <t>14.7</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>491.6</t>
+  </si>
+  <si>
+    <t>1960.1</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>19.6</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>320.9</t>
+  </si>
+  <si>
+    <t>2281.0</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>550.9</t>
+  </si>
+  <si>
+    <t>2831.9</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>526.9</t>
+  </si>
+  <si>
+    <t>3358.8</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>524.7</t>
+  </si>
+  <si>
+    <t>3883.5</t>
+  </si>
+  <si>
+    <t>38.8</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>446.7</t>
+  </si>
+  <si>
+    <t>4330.2</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>43.3</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>508.7</t>
+  </si>
+  <si>
+    <t>4838.9</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>373.0</t>
+  </si>
+  <si>
+    <t>5211.9</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>52.1</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>425.8</t>
+  </si>
+  <si>
+    <t>5637.7</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>56.4</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
+    <t>146.6</t>
+  </si>
+  <si>
+    <t>5784.3</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>57.8</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
+    <t>544.6</t>
+  </si>
+  <si>
+    <t>6328.9</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>63.3</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
+    <t>365.1</t>
+  </si>
+  <si>
+    <t>6694.0</t>
+  </si>
+  <si>
+    <t>66.9</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
+    <t>279.4</t>
+  </si>
+  <si>
+    <t>6973.4</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>69.7</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
+    <t>461.8</t>
+  </si>
+  <si>
+    <t>7435.2</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>74.4</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
+    <t>55.0</t>
+  </si>
+  <si>
+    <t>7490.2</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>74.9</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
+    <t>270.6</t>
+  </si>
+  <si>
+    <t>7760.8</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>77.6</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
+    <t>380.8</t>
+  </si>
+  <si>
+    <t>8141.6</t>
+  </si>
+  <si>
     <t>3.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>521.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>560.8</t>
-  </si>
-  <si>
-    <t>1082.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>10.8</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>386.2</t>
-  </si>
-  <si>
-    <t>1468.5</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>14.7</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>491.6</t>
-  </si>
-  <si>
-    <t>1960.1</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>19.6</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>320.9</t>
-  </si>
-  <si>
-    <t>2281.0</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>22.8</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>550.9</t>
-  </si>
-  <si>
-    <t>2831.9</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>526.9</t>
-  </si>
-  <si>
-    <t>3358.8</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>33.6</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>524.7</t>
-  </si>
-  <si>
-    <t>3883.5</t>
-  </si>
-  <si>
-    <t>38.8</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>446.7</t>
-  </si>
-  <si>
-    <t>4330.2</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>43.3</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>508.7</t>
-  </si>
-  <si>
-    <t>4838.9</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>373.0</t>
-  </si>
-  <si>
-    <t>5211.9</t>
-  </si>
-  <si>
-    <t>3.7</t>
-  </si>
-  <si>
-    <t>52.1</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>425.8</t>
-  </si>
-  <si>
-    <t>5637.7</t>
-  </si>
-  <si>
-    <t>4.3</t>
-  </si>
-  <si>
-    <t>56.4</t>
-  </si>
-  <si>
-    <t>13일</t>
-  </si>
-  <si>
-    <t>146.6</t>
-  </si>
-  <si>
-    <t>5784.3</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>57.8</t>
-  </si>
-  <si>
-    <t>14일</t>
-  </si>
-  <si>
-    <t>544.6</t>
-  </si>
-  <si>
-    <t>6328.9</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>63.3</t>
-  </si>
-  <si>
-    <t>15일</t>
-  </si>
-  <si>
-    <t>365.1</t>
-  </si>
-  <si>
-    <t>6694.0</t>
-  </si>
-  <si>
-    <t>66.9</t>
-  </si>
-  <si>
-    <t>16일</t>
-  </si>
-  <si>
-    <t>279.4</t>
-  </si>
-  <si>
-    <t>6973.4</t>
-  </si>
-  <si>
-    <t>2.8</t>
-  </si>
-  <si>
-    <t>69.7</t>
-  </si>
-  <si>
-    <t>17일</t>
-  </si>
-  <si>
-    <t>461.8</t>
-  </si>
-  <si>
-    <t>7435.2</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>74.4</t>
-  </si>
-  <si>
-    <t>18일</t>
-  </si>
-  <si>
-    <t>55.0</t>
-  </si>
-  <si>
-    <t>7490.2</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>74.9</t>
-  </si>
-  <si>
-    <t>19일</t>
-  </si>
-  <si>
-    <t>270.6</t>
-  </si>
-  <si>
-    <t>7760.8</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>77.6</t>
-  </si>
-  <si>
-    <t>20일</t>
-  </si>
-  <si>
-    <t>380.8</t>
-  </si>
-  <si>
-    <t>8141.6</t>
-  </si>
-  <si>
     <t>81.4</t>
   </si>
   <si>
@@ -419,10 +419,19 @@
     <t>27일</t>
   </si>
   <si>
+    <t>512.9</t>
+  </si>
+  <si>
+    <t>10409.4</t>
+  </si>
+  <si>
+    <t>104.1</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -788,10 +797,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -799,19 +808,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -819,19 +828,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -839,19 +848,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>35</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>36</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -859,19 +868,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>38</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>39</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>40</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>41</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -879,19 +888,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>43</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>44</v>
-      </c>
-      <c r="D10" t="s" s="37">
-        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
         <v>12</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -899,19 +908,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>47</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>48</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>49</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -919,19 +928,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>54</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -939,19 +948,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>59</v>
       </c>
-      <c r="E13" t="s" s="33">
+      <c r="F13" t="s" s="34">
         <v>60</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -959,19 +968,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>62</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>63</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>64</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -979,19 +988,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>69</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>70</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -999,19 +1008,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>72</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>73</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>74</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>75</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>76</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1019,19 +1028,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>77</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>78</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s" s="34">
         <v>79</v>
-      </c>
-      <c r="E17" t="s" s="33">
-        <v>60</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>80</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1039,19 +1048,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>81</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>82</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
         <v>83</v>
       </c>
-      <c r="E18" t="s" s="38">
+      <c r="F18" t="s" s="39">
         <v>84</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>85</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1059,19 +1068,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>86</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>87</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>88</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>89</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>90</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1079,19 +1088,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>91</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>92</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
         <v>93</v>
       </c>
-      <c r="E20" t="s" s="38">
+      <c r="F20" t="s" s="39">
         <v>94</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1099,19 +1108,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>96</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>97</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>98</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>99</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1119,16 +1128,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>101</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>102</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>103</v>
-      </c>
-      <c r="E22" t="s" s="38">
-        <v>9</v>
       </c>
       <c r="F22" t="s" s="39">
         <v>104</v>
@@ -1168,7 +1177,7 @@
         <v>112</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" t="s" s="39">
         <v>113</v>
@@ -1265,13 +1274,13 @@
         <v>135</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1279,19 +1288,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1299,19 +1308,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1319,19 +1328,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1339,19 +1348,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="146">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>385.5</t>
+    <t>390.0</t>
   </si>
   <si>
     <t>-</t>
@@ -431,10 +431,19 @@
     <t>28일</t>
   </si>
   <si>
+    <t>511.6</t>
+  </si>
+  <si>
+    <t>10921.0</t>
+  </si>
+  <si>
+    <t>109.2</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -1294,13 +1303,13 @@
         <v>139</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>139</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1308,19 +1317,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1328,19 +1337,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1348,19 +1357,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="150">
   <si>
     <t>No.</t>
   </si>
@@ -35,48 +35,51 @@
     <t>평균</t>
   </si>
   <si>
-    <t>390.0</t>
+    <t>379.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>521.5</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>560.8</t>
+  </si>
+  <si>
+    <t>1082.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>386.2</t>
+  </si>
+  <si>
+    <t>1468.5</t>
+  </si>
+  <si>
     <t>3.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>521.5</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>560.8</t>
-  </si>
-  <si>
-    <t>1082.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>10.8</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>386.2</t>
-  </si>
-  <si>
-    <t>1468.5</t>
-  </si>
-  <si>
     <t>14.7</t>
   </si>
   <si>
@@ -323,9 +326,6 @@
     <t>8141.6</t>
   </si>
   <si>
-    <t>3.8</t>
-  </si>
-  <si>
     <t>81.4</t>
   </si>
   <si>
@@ -443,10 +443,22 @@
     <t>29일</t>
   </si>
   <si>
+    <t>88.3</t>
+  </si>
+  <si>
+    <t>11009.3</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>110.1</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
   <si>
     <t>31일</t>
@@ -806,10 +818,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -817,19 +829,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -837,19 +849,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -857,19 +869,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -877,19 +889,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -897,19 +909,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
         <v>12</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -917,19 +929,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -937,19 +949,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -957,19 +969,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -977,19 +989,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -997,19 +1009,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -1017,19 +1029,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1037,19 +1049,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1057,19 +1069,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1077,19 +1089,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1097,19 +1109,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1117,19 +1129,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1137,16 +1149,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s" s="39">
         <v>104</v>
@@ -1186,7 +1198,7 @@
         <v>112</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s" s="39">
         <v>113</v>
@@ -1286,7 +1298,7 @@
         <v>136</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s" s="34">
         <v>137</v>
@@ -1306,7 +1318,7 @@
         <v>140</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F30" t="s" s="39">
         <v>141</v>
@@ -1323,13 +1335,13 @@
         <v>143</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1337,19 +1349,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1357,19 +1369,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="154">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>379.6</t>
+    <t>378.8</t>
   </si>
   <si>
     <t>-</t>
@@ -458,10 +458,22 @@
     <t>30일</t>
   </si>
   <si>
+    <t>355.3</t>
+  </si>
+  <si>
+    <t>11364.6</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>113.6</t>
+  </si>
+  <si>
+    <t>31일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>31일</t>
   </si>
 </sst>
 </file>
@@ -1355,13 +1367,13 @@
         <v>148</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1369,19 +1381,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-10-01.xlsx
+++ b/past_data/site_8023/2026-10-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="156">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>378.8</t>
+    <t>381.2</t>
   </si>
   <si>
     <t>-</t>
@@ -473,7 +473,13 @@
     <t>31일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>452.2</t>
+  </si>
+  <si>
+    <t>11816.8</t>
+  </si>
+  <si>
+    <t>118.2</t>
   </si>
 </sst>
 </file>
@@ -1387,13 +1393,13 @@
         <v>153</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
